--- a/Evidenta_grupei_curat_v2.xlsx
+++ b/Evidenta_grupei_curat_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Activitatea Didactica\Metodica\Excel_registru_electronic\Modificate\Cu delete\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Fizica\Programare\Python\Exercitii\PROIECTE\Evidenta_grupelor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EC8617C1-38CC-4F55-9C69-4AF07F6AA646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C782BCD-42ED-4674-9DE0-A60D3A22DDE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="759" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8964" tabRatio="759" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Curs" sheetId="1" r:id="rId1"/>
@@ -11997,7 +11997,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:T101"/>
+  <dimension ref="A1:T105"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.44140625" style="18" customWidth="1"/>
@@ -12108,25 +12108,25 @@
       <c r="T2" s="13"/>
     </row>
     <row r="3" spans="1:20" ht="18" x14ac:dyDescent="0.35">
-      <c r="A3" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B7)),Curs!B7,"")</f>
-        <v/>
+      <c r="A3" s="30">
+        <f>IF(NOT(ISBLANK(Curs!B3)),Curs!B3,"")</f>
+        <v>2</v>
       </c>
       <c r="B3" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C7)),Curs!C7,"")</f>
-        <v/>
+        <f>IF(NOT(ISBLANK(Curs!C3)),Curs!C3,"")</f>
+        <v>Nume, Prenume</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
       <c r="F3" s="10"/>
       <c r="G3" s="10"/>
-      <c r="H3" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C7)),ROUND(SUM(C3:G3),0),"")</f>
-        <v/>
+      <c r="H3" s="24">
+        <f>IF(NOT(ISBLANK(Curs!C3)),ROUND(SUM(C3:G3),0),"")</f>
+        <v>0</v>
       </c>
       <c r="I3" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C7)),
+        <f>IF(NOT(ISBLANK(Curs!C3)),
 IF(H3=0,"n/p",
 IF(AND(H3&gt;=$J$3,H3&lt;=$K$3),$L$3,
 IF(AND(H3&gt;=$J$4,H3&lt;=$K$4),$L$4,
@@ -12138,7 +12138,7 @@
 IF(AND(H3&gt;=$J$10,H3&lt;=$K$10),$L$10,
 IF(AND(H3&gt;=$J$11,H3&lt;=$K$11),$L$11)))))))))),
 "")</f>
-        <v/>
+        <v>n/p</v>
       </c>
       <c r="J3" s="22">
         <v>0</v>
@@ -12164,25 +12164,25 @@
       <c r="T3" s="13"/>
     </row>
     <row r="4" spans="1:20" ht="18" x14ac:dyDescent="0.35">
-      <c r="A4" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B8)),Curs!B8,"")</f>
-        <v/>
+      <c r="A4" s="30">
+        <f>IF(NOT(ISBLANK(Curs!B4)),Curs!B4,"")</f>
+        <v>3</v>
       </c>
       <c r="B4" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C8)),Curs!C8,"")</f>
-        <v/>
+        <f>IF(NOT(ISBLANK(Curs!C4)),Curs!C4,"")</f>
+        <v>Nume, Prenume</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
       <c r="G4" s="10"/>
-      <c r="H4" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C8)),ROUND(SUM(C4:G4),0),"")</f>
-        <v/>
+      <c r="H4" s="24">
+        <f>IF(NOT(ISBLANK(Curs!C4)),ROUND(SUM(C4:G4),0),"")</f>
+        <v>0</v>
       </c>
       <c r="I4" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C8)),
+        <f>IF(NOT(ISBLANK(Curs!C4)),
 IF(H4=0,"n/p",
 IF(AND(H4&gt;=$J$3,H4&lt;=$K$3),$L$3,
 IF(AND(H4&gt;=$J$4,H4&lt;=$K$4),$L$4,
@@ -12194,7 +12194,7 @@
 IF(AND(H4&gt;=$J$10,H4&lt;=$K$10),$L$10,
 IF(AND(H4&gt;=$J$11,H4&lt;=$K$11),$L$11)))))))))),
 "")</f>
-        <v/>
+        <v>n/p</v>
       </c>
       <c r="J4" s="22">
         <v>4</v>
@@ -12221,11 +12221,11 @@
     </row>
     <row r="5" spans="1:20" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B9)),Curs!B9,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B5)),Curs!B5,"")</f>
         <v/>
       </c>
       <c r="B5" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C9)),Curs!C9,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C5)),Curs!C5,"")</f>
         <v/>
       </c>
       <c r="C5" s="10"/>
@@ -12234,11 +12234,11 @@
       <c r="F5" s="10"/>
       <c r="G5" s="10"/>
       <c r="H5" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C9)),ROUND(SUM(C5:G5),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C5)),ROUND(SUM(C5:G5),0),"")</f>
         <v/>
       </c>
       <c r="I5" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C9)),
+        <f>IF(NOT(ISBLANK(Curs!C5)),
 IF(H5=0,"n/p",
 IF(AND(H5&gt;=$J$3,H5&lt;=$K$3),$L$3,
 IF(AND(H5&gt;=$J$4,H5&lt;=$K$4),$L$4,
@@ -12277,11 +12277,11 @@
     </row>
     <row r="6" spans="1:20" ht="18" x14ac:dyDescent="0.35">
       <c r="A6" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B10)),Curs!B10,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B6)),Curs!B6,"")</f>
         <v/>
       </c>
       <c r="B6" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C10)),Curs!C10,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C6)),Curs!C6,"")</f>
         <v/>
       </c>
       <c r="C6" s="10"/>
@@ -12290,11 +12290,11 @@
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
       <c r="H6" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C10)),ROUND(SUM(C6:G6),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C6)),ROUND(SUM(C6:G6),0),"")</f>
         <v/>
       </c>
       <c r="I6" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C10)),
+        <f>IF(NOT(ISBLANK(Curs!C6)),
 IF(H6=0,"n/p",
 IF(AND(H6&gt;=$J$3,H6&lt;=$K$3),$L$3,
 IF(AND(H6&gt;=$J$4,H6&lt;=$K$4),$L$4,
@@ -12333,11 +12333,11 @@
     </row>
     <row r="7" spans="1:20" ht="18" x14ac:dyDescent="0.35">
       <c r="A7" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B11)),Curs!B11,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B7)),Curs!B7,"")</f>
         <v/>
       </c>
       <c r="B7" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C11)),Curs!C11,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C7)),Curs!C7,"")</f>
         <v/>
       </c>
       <c r="C7" s="10"/>
@@ -12346,11 +12346,11 @@
       <c r="F7" s="10"/>
       <c r="G7" s="10"/>
       <c r="H7" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C11)),ROUND(SUM(C7:G7),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C7)),ROUND(SUM(C7:G7),0),"")</f>
         <v/>
       </c>
       <c r="I7" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C11)),
+        <f>IF(NOT(ISBLANK(Curs!C7)),
 IF(H7=0,"n/p",
 IF(AND(H7&gt;=$J$3,H7&lt;=$K$3),$L$3,
 IF(AND(H7&gt;=$J$4,H7&lt;=$K$4),$L$4,
@@ -12389,11 +12389,11 @@
     </row>
     <row r="8" spans="1:20" ht="18" x14ac:dyDescent="0.35">
       <c r="A8" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B12)),Curs!B12,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B8)),Curs!B8,"")</f>
         <v/>
       </c>
       <c r="B8" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C12)),Curs!C12,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C8)),Curs!C8,"")</f>
         <v/>
       </c>
       <c r="C8" s="10"/>
@@ -12402,11 +12402,11 @@
       <c r="F8" s="10"/>
       <c r="G8" s="10"/>
       <c r="H8" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C12)),ROUND(SUM(C8:G8),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C8)),ROUND(SUM(C8:G8),0),"")</f>
         <v/>
       </c>
       <c r="I8" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C12)),
+        <f>IF(NOT(ISBLANK(Curs!C8)),
 IF(H8=0,"n/p",
 IF(AND(H8&gt;=$J$3,H8&lt;=$K$3),$L$3,
 IF(AND(H8&gt;=$J$4,H8&lt;=$K$4),$L$4,
@@ -12445,11 +12445,11 @@
     </row>
     <row r="9" spans="1:20" ht="18" x14ac:dyDescent="0.35">
       <c r="A9" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B13)),Curs!B13,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B9)),Curs!B9,"")</f>
         <v/>
       </c>
       <c r="B9" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C13)),Curs!C13,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C9)),Curs!C9,"")</f>
         <v/>
       </c>
       <c r="C9" s="10"/>
@@ -12458,11 +12458,11 @@
       <c r="F9" s="10"/>
       <c r="G9" s="10"/>
       <c r="H9" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C13)),ROUND(SUM(C9:G9),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C9)),ROUND(SUM(C9:G9),0),"")</f>
         <v/>
       </c>
       <c r="I9" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C13)),
+        <f>IF(NOT(ISBLANK(Curs!C9)),
 IF(H9=0,"n/p",
 IF(AND(H9&gt;=$J$3,H9&lt;=$K$3),$L$3,
 IF(AND(H9&gt;=$J$4,H9&lt;=$K$4),$L$4,
@@ -12501,11 +12501,11 @@
     </row>
     <row r="10" spans="1:20" ht="18" x14ac:dyDescent="0.35">
       <c r="A10" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B14)),Curs!B14,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B10)),Curs!B10,"")</f>
         <v/>
       </c>
       <c r="B10" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C14)),Curs!C14,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C10)),Curs!C10,"")</f>
         <v/>
       </c>
       <c r="C10" s="10"/>
@@ -12514,11 +12514,11 @@
       <c r="F10" s="10"/>
       <c r="G10" s="10"/>
       <c r="H10" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C14)),ROUND(SUM(C10:G10),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C10)),ROUND(SUM(C10:G10),0),"")</f>
         <v/>
       </c>
       <c r="I10" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C14)),
+        <f>IF(NOT(ISBLANK(Curs!C10)),
 IF(H10=0,"n/p",
 IF(AND(H10&gt;=$J$3,H10&lt;=$K$3),$L$3,
 IF(AND(H10&gt;=$J$4,H10&lt;=$K$4),$L$4,
@@ -12557,11 +12557,11 @@
     </row>
     <row r="11" spans="1:20" ht="18" x14ac:dyDescent="0.35">
       <c r="A11" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B15)),Curs!B15,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B11)),Curs!B11,"")</f>
         <v/>
       </c>
       <c r="B11" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C15)),Curs!C15,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C11)),Curs!C11,"")</f>
         <v/>
       </c>
       <c r="C11" s="10"/>
@@ -12570,11 +12570,11 @@
       <c r="F11" s="10"/>
       <c r="G11" s="10"/>
       <c r="H11" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C15)),ROUND(SUM(C11:G11),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C11)),ROUND(SUM(C11:G11),0),"")</f>
         <v/>
       </c>
       <c r="I11" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C15)),
+        <f>IF(NOT(ISBLANK(Curs!C11)),
 IF(H11=0,"n/p",
 IF(AND(H11&gt;=$J$3,H11&lt;=$K$3),$L$3,
 IF(AND(H11&gt;=$J$4,H11&lt;=$K$4),$L$4,
@@ -12613,11 +12613,11 @@
     </row>
     <row r="12" spans="1:20" ht="18" x14ac:dyDescent="0.35">
       <c r="A12" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B16)),Curs!B16,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B12)),Curs!B12,"")</f>
         <v/>
       </c>
       <c r="B12" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C16)),Curs!C16,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C12)),Curs!C12,"")</f>
         <v/>
       </c>
       <c r="C12" s="10"/>
@@ -12626,11 +12626,11 @@
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
       <c r="H12" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C16)),ROUND(SUM(C12:G12),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C12)),ROUND(SUM(C12:G12),0),"")</f>
         <v/>
       </c>
       <c r="I12" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C16)),
+        <f>IF(NOT(ISBLANK(Curs!C12)),
 IF(H12=0,"n/p",
 IF(AND(H12&gt;=$J$3,H12&lt;=$K$3),$L$3,
 IF(AND(H12&gt;=$J$4,H12&lt;=$K$4),$L$4,
@@ -12663,11 +12663,11 @@
     </row>
     <row r="13" spans="1:20" ht="18" x14ac:dyDescent="0.35">
       <c r="A13" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B17)),Curs!B17,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B13)),Curs!B13,"")</f>
         <v/>
       </c>
       <c r="B13" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C17)),Curs!C17,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C13)),Curs!C13,"")</f>
         <v/>
       </c>
       <c r="C13" s="10"/>
@@ -12676,11 +12676,11 @@
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
       <c r="H13" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C17)),ROUND(SUM(C13:G13),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C13)),ROUND(SUM(C13:G13),0),"")</f>
         <v/>
       </c>
       <c r="I13" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C17)),
+        <f>IF(NOT(ISBLANK(Curs!C13)),
 IF(H13=0,"n/p",
 IF(AND(H13&gt;=$J$3,H13&lt;=$K$3),$L$3,
 IF(AND(H13&gt;=$J$4,H13&lt;=$K$4),$L$4,
@@ -12702,7 +12702,7 @@
       </c>
       <c r="N13" s="27">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O13" s="8"/>
       <c r="P13" s="13"/>
@@ -12713,11 +12713,11 @@
     </row>
     <row r="14" spans="1:20" ht="18" x14ac:dyDescent="0.35">
       <c r="A14" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B18)),Curs!B18,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B14)),Curs!B14,"")</f>
         <v/>
       </c>
       <c r="B14" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C18)),Curs!C18,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C14)),Curs!C14,"")</f>
         <v/>
       </c>
       <c r="C14" s="10"/>
@@ -12726,11 +12726,11 @@
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
       <c r="H14" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C18)),ROUND(SUM(C14:G14),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C14)),ROUND(SUM(C14:G14),0),"")</f>
         <v/>
       </c>
       <c r="I14" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C18)),
+        <f>IF(NOT(ISBLANK(Curs!C14)),
 IF(H14=0,"n/p",
 IF(AND(H14&gt;=$J$3,H14&lt;=$K$3),$L$3,
 IF(AND(H14&gt;=$J$4,H14&lt;=$K$4),$L$4,
@@ -12755,11 +12755,11 @@
     </row>
     <row r="15" spans="1:20" ht="18" x14ac:dyDescent="0.35">
       <c r="A15" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B19)),Curs!B19,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B15)),Curs!B15,"")</f>
         <v/>
       </c>
       <c r="B15" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C19)),Curs!C19,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C15)),Curs!C15,"")</f>
         <v/>
       </c>
       <c r="C15" s="10"/>
@@ -12768,11 +12768,11 @@
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
       <c r="H15" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C19)),ROUND(SUM(C15:G15),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C15)),ROUND(SUM(C15:G15),0),"")</f>
         <v/>
       </c>
       <c r="I15" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C19)),
+        <f>IF(NOT(ISBLANK(Curs!C15)),
 IF(H15=0,"n/p",
 IF(AND(H15&gt;=$J$3,H15&lt;=$K$3),$L$3,
 IF(AND(H15&gt;=$J$4,H15&lt;=$K$4),$L$4,
@@ -12794,11 +12794,11 @@
     </row>
     <row r="16" spans="1:20" ht="18" x14ac:dyDescent="0.35">
       <c r="A16" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B20)),Curs!B20,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B16)),Curs!B16,"")</f>
         <v/>
       </c>
       <c r="B16" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C20)),Curs!C20,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C16)),Curs!C16,"")</f>
         <v/>
       </c>
       <c r="C16" s="10"/>
@@ -12807,11 +12807,11 @@
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
       <c r="H16" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C20)),ROUND(SUM(C16:G16),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C16)),ROUND(SUM(C16:G16),0),"")</f>
         <v/>
       </c>
       <c r="I16" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C20)),
+        <f>IF(NOT(ISBLANK(Curs!C16)),
 IF(H16=0,"n/p",
 IF(AND(H16&gt;=$J$3,H16&lt;=$K$3),$L$3,
 IF(AND(H16&gt;=$J$4,H16&lt;=$K$4),$L$4,
@@ -12833,11 +12833,11 @@
     </row>
     <row r="17" spans="1:18" ht="18" x14ac:dyDescent="0.35">
       <c r="A17" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B21)),Curs!B21,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B17)),Curs!B17,"")</f>
         <v/>
       </c>
       <c r="B17" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C21)),Curs!C21,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C17)),Curs!C17,"")</f>
         <v/>
       </c>
       <c r="C17" s="10"/>
@@ -12846,11 +12846,11 @@
       <c r="F17" s="10"/>
       <c r="G17" s="10"/>
       <c r="H17" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C21)),ROUND(SUM(C17:G17),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C17)),ROUND(SUM(C17:G17),0),"")</f>
         <v/>
       </c>
       <c r="I17" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C21)),
+        <f>IF(NOT(ISBLANK(Curs!C17)),
 IF(H17=0,"n/p",
 IF(AND(H17&gt;=$J$3,H17&lt;=$K$3),$L$3,
 IF(AND(H17&gt;=$J$4,H17&lt;=$K$4),$L$4,
@@ -12872,11 +12872,11 @@
     </row>
     <row r="18" spans="1:18" ht="18" x14ac:dyDescent="0.35">
       <c r="A18" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B22)),Curs!B22,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B18)),Curs!B18,"")</f>
         <v/>
       </c>
       <c r="B18" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C22)),Curs!C22,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C18)),Curs!C18,"")</f>
         <v/>
       </c>
       <c r="C18" s="10"/>
@@ -12885,11 +12885,11 @@
       <c r="F18" s="10"/>
       <c r="G18" s="10"/>
       <c r="H18" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C22)),ROUND(SUM(C18:G18),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C18)),ROUND(SUM(C18:G18),0),"")</f>
         <v/>
       </c>
       <c r="I18" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C22)),
+        <f>IF(NOT(ISBLANK(Curs!C18)),
 IF(H18=0,"n/p",
 IF(AND(H18&gt;=$J$3,H18&lt;=$K$3),$L$3,
 IF(AND(H18&gt;=$J$4,H18&lt;=$K$4),$L$4,
@@ -12911,11 +12911,11 @@
     </row>
     <row r="19" spans="1:18" ht="18" x14ac:dyDescent="0.35">
       <c r="A19" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B23)),Curs!B23,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B19)),Curs!B19,"")</f>
         <v/>
       </c>
       <c r="B19" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C23)),Curs!C23,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C19)),Curs!C19,"")</f>
         <v/>
       </c>
       <c r="C19" s="10"/>
@@ -12924,11 +12924,11 @@
       <c r="F19" s="10"/>
       <c r="G19" s="10"/>
       <c r="H19" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C23)),ROUND(SUM(C19:G19),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C19)),ROUND(SUM(C19:G19),0),"")</f>
         <v/>
       </c>
       <c r="I19" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C23)),
+        <f>IF(NOT(ISBLANK(Curs!C19)),
 IF(H19=0,"n/p",
 IF(AND(H19&gt;=$J$3,H19&lt;=$K$3),$L$3,
 IF(AND(H19&gt;=$J$4,H19&lt;=$K$4),$L$4,
@@ -12950,11 +12950,11 @@
     </row>
     <row r="20" spans="1:18" ht="18" x14ac:dyDescent="0.35">
       <c r="A20" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B24)),Curs!B24,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B20)),Curs!B20,"")</f>
         <v/>
       </c>
       <c r="B20" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C24)),Curs!C24,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C20)),Curs!C20,"")</f>
         <v/>
       </c>
       <c r="C20" s="10"/>
@@ -12963,11 +12963,11 @@
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
       <c r="H20" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C24)),ROUND(SUM(C20:G20),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C20)),ROUND(SUM(C20:G20),0),"")</f>
         <v/>
       </c>
       <c r="I20" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C24)),
+        <f>IF(NOT(ISBLANK(Curs!C20)),
 IF(H20=0,"n/p",
 IF(AND(H20&gt;=$J$3,H20&lt;=$K$3),$L$3,
 IF(AND(H20&gt;=$J$4,H20&lt;=$K$4),$L$4,
@@ -12989,11 +12989,11 @@
     </row>
     <row r="21" spans="1:18" ht="18" x14ac:dyDescent="0.35">
       <c r="A21" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B25)),Curs!B25,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B21)),Curs!B21,"")</f>
         <v/>
       </c>
       <c r="B21" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C25)),Curs!C25,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C21)),Curs!C21,"")</f>
         <v/>
       </c>
       <c r="C21" s="10"/>
@@ -13002,11 +13002,11 @@
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
       <c r="H21" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C25)),ROUND(SUM(C21:G21),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C21)),ROUND(SUM(C21:G21),0),"")</f>
         <v/>
       </c>
       <c r="I21" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C25)),
+        <f>IF(NOT(ISBLANK(Curs!C21)),
 IF(H21=0,"n/p",
 IF(AND(H21&gt;=$J$3,H21&lt;=$K$3),$L$3,
 IF(AND(H21&gt;=$J$4,H21&lt;=$K$4),$L$4,
@@ -13028,11 +13028,11 @@
     </row>
     <row r="22" spans="1:18" ht="18" x14ac:dyDescent="0.35">
       <c r="A22" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B26)),Curs!B26,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B22)),Curs!B22,"")</f>
         <v/>
       </c>
       <c r="B22" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C26)),Curs!C26,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C22)),Curs!C22,"")</f>
         <v/>
       </c>
       <c r="C22" s="10"/>
@@ -13041,11 +13041,11 @@
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
       <c r="H22" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C26)),ROUND(SUM(C22:G22),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C22)),ROUND(SUM(C22:G22),0),"")</f>
         <v/>
       </c>
       <c r="I22" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C26)),
+        <f>IF(NOT(ISBLANK(Curs!C22)),
 IF(H22=0,"n/p",
 IF(AND(H22&gt;=$J$3,H22&lt;=$K$3),$L$3,
 IF(AND(H22&gt;=$J$4,H22&lt;=$K$4),$L$4,
@@ -13067,11 +13067,11 @@
     </row>
     <row r="23" spans="1:18" ht="18" x14ac:dyDescent="0.35">
       <c r="A23" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B27)),Curs!B27,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B23)),Curs!B23,"")</f>
         <v/>
       </c>
       <c r="B23" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C27)),Curs!C27,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C23)),Curs!C23,"")</f>
         <v/>
       </c>
       <c r="C23" s="10"/>
@@ -13080,11 +13080,11 @@
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
       <c r="H23" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C27)),ROUND(SUM(C23:G23),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C23)),ROUND(SUM(C23:G23),0),"")</f>
         <v/>
       </c>
       <c r="I23" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C27)),
+        <f>IF(NOT(ISBLANK(Curs!C23)),
 IF(H23=0,"n/p",
 IF(AND(H23&gt;=$J$3,H23&lt;=$K$3),$L$3,
 IF(AND(H23&gt;=$J$4,H23&lt;=$K$4),$L$4,
@@ -13106,11 +13106,11 @@
     </row>
     <row r="24" spans="1:18" ht="18" x14ac:dyDescent="0.35">
       <c r="A24" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B28)),Curs!B28,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B24)),Curs!B24,"")</f>
         <v/>
       </c>
       <c r="B24" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C28)),Curs!C28,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C24)),Curs!C24,"")</f>
         <v/>
       </c>
       <c r="C24" s="10"/>
@@ -13119,11 +13119,11 @@
       <c r="F24" s="10"/>
       <c r="G24" s="10"/>
       <c r="H24" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C28)),ROUND(SUM(C24:G24),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C24)),ROUND(SUM(C24:G24),0),"")</f>
         <v/>
       </c>
       <c r="I24" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C28)),
+        <f>IF(NOT(ISBLANK(Curs!C24)),
 IF(H24=0,"n/p",
 IF(AND(H24&gt;=$J$3,H24&lt;=$K$3),$L$3,
 IF(AND(H24&gt;=$J$4,H24&lt;=$K$4),$L$4,
@@ -13145,11 +13145,11 @@
     </row>
     <row r="25" spans="1:18" ht="18" x14ac:dyDescent="0.35">
       <c r="A25" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B29)),Curs!B29,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B25)),Curs!B25,"")</f>
         <v/>
       </c>
       <c r="B25" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C29)),Curs!C29,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C25)),Curs!C25,"")</f>
         <v/>
       </c>
       <c r="C25" s="10"/>
@@ -13158,11 +13158,11 @@
       <c r="F25" s="10"/>
       <c r="G25" s="10"/>
       <c r="H25" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C29)),ROUND(SUM(C25:G25),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C25)),ROUND(SUM(C25:G25),0),"")</f>
         <v/>
       </c>
       <c r="I25" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C29)),
+        <f>IF(NOT(ISBLANK(Curs!C25)),
 IF(H25=0,"n/p",
 IF(AND(H25&gt;=$J$3,H25&lt;=$K$3),$L$3,
 IF(AND(H25&gt;=$J$4,H25&lt;=$K$4),$L$4,
@@ -13184,11 +13184,11 @@
     </row>
     <row r="26" spans="1:18" ht="18" x14ac:dyDescent="0.35">
       <c r="A26" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B30)),Curs!B30,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B26)),Curs!B26,"")</f>
         <v/>
       </c>
       <c r="B26" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C30)),Curs!C30,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C26)),Curs!C26,"")</f>
         <v/>
       </c>
       <c r="C26" s="10"/>
@@ -13197,11 +13197,11 @@
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
       <c r="H26" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C30)),ROUND(SUM(C26:G26),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C26)),ROUND(SUM(C26:G26),0),"")</f>
         <v/>
       </c>
       <c r="I26" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C30)),
+        <f>IF(NOT(ISBLANK(Curs!C26)),
 IF(H26=0,"n/p",
 IF(AND(H26&gt;=$J$3,H26&lt;=$K$3),$L$3,
 IF(AND(H26&gt;=$J$4,H26&lt;=$K$4),$L$4,
@@ -13223,11 +13223,11 @@
     </row>
     <row r="27" spans="1:18" ht="18" x14ac:dyDescent="0.35">
       <c r="A27" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B31)),Curs!B31,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B27)),Curs!B27,"")</f>
         <v/>
       </c>
       <c r="B27" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C31)),Curs!C31,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C27)),Curs!C27,"")</f>
         <v/>
       </c>
       <c r="C27" s="10"/>
@@ -13236,11 +13236,11 @@
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
       <c r="H27" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C31)),ROUND(SUM(C27:G27),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C27)),ROUND(SUM(C27:G27),0),"")</f>
         <v/>
       </c>
       <c r="I27" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C31)),
+        <f>IF(NOT(ISBLANK(Curs!C27)),
 IF(H27=0,"n/p",
 IF(AND(H27&gt;=$J$3,H27&lt;=$K$3),$L$3,
 IF(AND(H27&gt;=$J$4,H27&lt;=$K$4),$L$4,
@@ -13266,11 +13266,11 @@
     </row>
     <row r="28" spans="1:18" ht="18" x14ac:dyDescent="0.35">
       <c r="A28" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B32)),Curs!B32,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B28)),Curs!B28,"")</f>
         <v/>
       </c>
       <c r="B28" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C32)),Curs!C32,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C28)),Curs!C28,"")</f>
         <v/>
       </c>
       <c r="C28" s="10"/>
@@ -13279,11 +13279,11 @@
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
       <c r="H28" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C32)),ROUND(SUM(C28:G28),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C28)),ROUND(SUM(C28:G28),0),"")</f>
         <v/>
       </c>
       <c r="I28" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C32)),
+        <f>IF(NOT(ISBLANK(Curs!C28)),
 IF(H28=0,"n/p",
 IF(AND(H28&gt;=$J$3,H28&lt;=$K$3),$L$3,
 IF(AND(H28&gt;=$J$4,H28&lt;=$K$4),$L$4,
@@ -13300,11 +13300,11 @@
     </row>
     <row r="29" spans="1:18" ht="18" x14ac:dyDescent="0.35">
       <c r="A29" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B33)),Curs!B33,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B29)),Curs!B29,"")</f>
         <v/>
       </c>
       <c r="B29" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C33)),Curs!C33,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C29)),Curs!C29,"")</f>
         <v/>
       </c>
       <c r="C29" s="10"/>
@@ -13313,11 +13313,11 @@
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
       <c r="H29" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C33)),ROUND(SUM(C29:G29),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C29)),ROUND(SUM(C29:G29),0),"")</f>
         <v/>
       </c>
       <c r="I29" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C33)),
+        <f>IF(NOT(ISBLANK(Curs!C29)),
 IF(H29=0,"n/p",
 IF(AND(H29&gt;=$J$3,H29&lt;=$K$3),$L$3,
 IF(AND(H29&gt;=$J$4,H29&lt;=$K$4),$L$4,
@@ -13334,11 +13334,11 @@
     </row>
     <row r="30" spans="1:18" ht="18" x14ac:dyDescent="0.35">
       <c r="A30" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B34)),Curs!B34,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B30)),Curs!B30,"")</f>
         <v/>
       </c>
       <c r="B30" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C34)),Curs!C34,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C30)),Curs!C30,"")</f>
         <v/>
       </c>
       <c r="C30" s="10"/>
@@ -13347,11 +13347,11 @@
       <c r="F30" s="10"/>
       <c r="G30" s="10"/>
       <c r="H30" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C34)),ROUND(SUM(C30:G30),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C30)),ROUND(SUM(C30:G30),0),"")</f>
         <v/>
       </c>
       <c r="I30" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C34)),
+        <f>IF(NOT(ISBLANK(Curs!C30)),
 IF(H30=0,"n/p",
 IF(AND(H30&gt;=$J$3,H30&lt;=$K$3),$L$3,
 IF(AND(H30&gt;=$J$4,H30&lt;=$K$4),$L$4,
@@ -13368,11 +13368,11 @@
     </row>
     <row r="31" spans="1:18" ht="18" x14ac:dyDescent="0.35">
       <c r="A31" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B35)),Curs!B35,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B31)),Curs!B31,"")</f>
         <v/>
       </c>
       <c r="B31" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C35)),Curs!C35,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C31)),Curs!C31,"")</f>
         <v/>
       </c>
       <c r="C31" s="10"/>
@@ -13381,11 +13381,11 @@
       <c r="F31" s="10"/>
       <c r="G31" s="10"/>
       <c r="H31" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C35)),ROUND(SUM(C31:G31),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C31)),ROUND(SUM(C31:G31),0),"")</f>
         <v/>
       </c>
       <c r="I31" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C35)),
+        <f>IF(NOT(ISBLANK(Curs!C31)),
 IF(H31=0,"n/p",
 IF(AND(H31&gt;=$J$3,H31&lt;=$K$3),$L$3,
 IF(AND(H31&gt;=$J$4,H31&lt;=$K$4),$L$4,
@@ -13402,11 +13402,11 @@
     </row>
     <row r="32" spans="1:18" ht="18" x14ac:dyDescent="0.35">
       <c r="A32" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B36)),Curs!B36,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B32)),Curs!B32,"")</f>
         <v/>
       </c>
       <c r="B32" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C36)),Curs!C36,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C32)),Curs!C32,"")</f>
         <v/>
       </c>
       <c r="C32" s="10"/>
@@ -13415,11 +13415,11 @@
       <c r="F32" s="10"/>
       <c r="G32" s="10"/>
       <c r="H32" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C36)),ROUND(SUM(C32:G32),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C32)),ROUND(SUM(C32:G32),0),"")</f>
         <v/>
       </c>
       <c r="I32" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C36)),
+        <f>IF(NOT(ISBLANK(Curs!C32)),
 IF(H32=0,"n/p",
 IF(AND(H32&gt;=$J$3,H32&lt;=$K$3),$L$3,
 IF(AND(H32&gt;=$J$4,H32&lt;=$K$4),$L$4,
@@ -13436,11 +13436,11 @@
     </row>
     <row r="33" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A33" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B37)),Curs!B37,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B33)),Curs!B33,"")</f>
         <v/>
       </c>
       <c r="B33" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C37)),Curs!C37,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C33)),Curs!C33,"")</f>
         <v/>
       </c>
       <c r="C33" s="10"/>
@@ -13449,11 +13449,11 @@
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
       <c r="H33" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C37)),ROUND(SUM(C33:G33),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C33)),ROUND(SUM(C33:G33),0),"")</f>
         <v/>
       </c>
       <c r="I33" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C37)),
+        <f>IF(NOT(ISBLANK(Curs!C33)),
 IF(H33=0,"n/p",
 IF(AND(H33&gt;=$J$3,H33&lt;=$K$3),$L$3,
 IF(AND(H33&gt;=$J$4,H33&lt;=$K$4),$L$4,
@@ -13470,11 +13470,11 @@
     </row>
     <row r="34" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A34" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B38)),Curs!B38,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B34)),Curs!B34,"")</f>
         <v/>
       </c>
       <c r="B34" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C38)),Curs!C38,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C34)),Curs!C34,"")</f>
         <v/>
       </c>
       <c r="C34" s="10"/>
@@ -13483,11 +13483,11 @@
       <c r="F34" s="10"/>
       <c r="G34" s="10"/>
       <c r="H34" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C38)),ROUND(SUM(C34:G34),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C34)),ROUND(SUM(C34:G34),0),"")</f>
         <v/>
       </c>
       <c r="I34" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C38)),
+        <f>IF(NOT(ISBLANK(Curs!C34)),
 IF(H34=0,"n/p",
 IF(AND(H34&gt;=$J$3,H34&lt;=$K$3),$L$3,
 IF(AND(H34&gt;=$J$4,H34&lt;=$K$4),$L$4,
@@ -13504,11 +13504,11 @@
     </row>
     <row r="35" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A35" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B39)),Curs!B39,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B35)),Curs!B35,"")</f>
         <v/>
       </c>
       <c r="B35" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C39)),Curs!C39,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C35)),Curs!C35,"")</f>
         <v/>
       </c>
       <c r="C35" s="10"/>
@@ -13517,11 +13517,11 @@
       <c r="F35" s="10"/>
       <c r="G35" s="10"/>
       <c r="H35" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C39)),ROUND(SUM(C35:G35),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C35)),ROUND(SUM(C35:G35),0),"")</f>
         <v/>
       </c>
       <c r="I35" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C39)),
+        <f>IF(NOT(ISBLANK(Curs!C35)),
 IF(H35=0,"n/p",
 IF(AND(H35&gt;=$J$3,H35&lt;=$K$3),$L$3,
 IF(AND(H35&gt;=$J$4,H35&lt;=$K$4),$L$4,
@@ -13538,11 +13538,11 @@
     </row>
     <row r="36" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A36" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B40)),Curs!B40,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B36)),Curs!B36,"")</f>
         <v/>
       </c>
       <c r="B36" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C40)),Curs!C40,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C36)),Curs!C36,"")</f>
         <v/>
       </c>
       <c r="C36" s="10"/>
@@ -13551,11 +13551,11 @@
       <c r="F36" s="10"/>
       <c r="G36" s="10"/>
       <c r="H36" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C40)),ROUND(SUM(C36:G36),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C36)),ROUND(SUM(C36:G36),0),"")</f>
         <v/>
       </c>
       <c r="I36" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C40)),
+        <f>IF(NOT(ISBLANK(Curs!C36)),
 IF(H36=0,"n/p",
 IF(AND(H36&gt;=$J$3,H36&lt;=$K$3),$L$3,
 IF(AND(H36&gt;=$J$4,H36&lt;=$K$4),$L$4,
@@ -13572,11 +13572,11 @@
     </row>
     <row r="37" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A37" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B41)),Curs!B41,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B37)),Curs!B37,"")</f>
         <v/>
       </c>
       <c r="B37" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C41)),Curs!C41,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C37)),Curs!C37,"")</f>
         <v/>
       </c>
       <c r="C37" s="10"/>
@@ -13585,11 +13585,11 @@
       <c r="F37" s="10"/>
       <c r="G37" s="10"/>
       <c r="H37" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C41)),ROUND(SUM(C37:G37),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C37)),ROUND(SUM(C37:G37),0),"")</f>
         <v/>
       </c>
       <c r="I37" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C41)),
+        <f>IF(NOT(ISBLANK(Curs!C37)),
 IF(H37=0,"n/p",
 IF(AND(H37&gt;=$J$3,H37&lt;=$K$3),$L$3,
 IF(AND(H37&gt;=$J$4,H37&lt;=$K$4),$L$4,
@@ -13606,11 +13606,11 @@
     </row>
     <row r="38" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A38" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B42)),Curs!B42,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B38)),Curs!B38,"")</f>
         <v/>
       </c>
       <c r="B38" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C42)),Curs!C42,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C38)),Curs!C38,"")</f>
         <v/>
       </c>
       <c r="C38" s="10"/>
@@ -13619,11 +13619,11 @@
       <c r="F38" s="10"/>
       <c r="G38" s="10"/>
       <c r="H38" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C42)),ROUND(SUM(C38:G38),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C38)),ROUND(SUM(C38:G38),0),"")</f>
         <v/>
       </c>
       <c r="I38" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C42)),
+        <f>IF(NOT(ISBLANK(Curs!C38)),
 IF(H38=0,"n/p",
 IF(AND(H38&gt;=$J$3,H38&lt;=$K$3),$L$3,
 IF(AND(H38&gt;=$J$4,H38&lt;=$K$4),$L$4,
@@ -13640,11 +13640,11 @@
     </row>
     <row r="39" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A39" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B43)),Curs!B43,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B39)),Curs!B39,"")</f>
         <v/>
       </c>
       <c r="B39" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C43)),Curs!C43,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C39)),Curs!C39,"")</f>
         <v/>
       </c>
       <c r="C39" s="10"/>
@@ -13653,11 +13653,11 @@
       <c r="F39" s="10"/>
       <c r="G39" s="10"/>
       <c r="H39" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C43)),ROUND(SUM(C39:G39),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C39)),ROUND(SUM(C39:G39),0),"")</f>
         <v/>
       </c>
       <c r="I39" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C43)),
+        <f>IF(NOT(ISBLANK(Curs!C39)),
 IF(H39=0,"n/p",
 IF(AND(H39&gt;=$J$3,H39&lt;=$K$3),$L$3,
 IF(AND(H39&gt;=$J$4,H39&lt;=$K$4),$L$4,
@@ -13674,11 +13674,11 @@
     </row>
     <row r="40" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A40" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B44)),Curs!B44,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B40)),Curs!B40,"")</f>
         <v/>
       </c>
       <c r="B40" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C44)),Curs!C44,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C40)),Curs!C40,"")</f>
         <v/>
       </c>
       <c r="C40" s="10"/>
@@ -13687,11 +13687,11 @@
       <c r="F40" s="10"/>
       <c r="G40" s="10"/>
       <c r="H40" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C44)),ROUND(SUM(C40:G40),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C40)),ROUND(SUM(C40:G40),0),"")</f>
         <v/>
       </c>
       <c r="I40" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C44)),
+        <f>IF(NOT(ISBLANK(Curs!C40)),
 IF(H40=0,"n/p",
 IF(AND(H40&gt;=$J$3,H40&lt;=$K$3),$L$3,
 IF(AND(H40&gt;=$J$4,H40&lt;=$K$4),$L$4,
@@ -13708,11 +13708,11 @@
     </row>
     <row r="41" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A41" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B45)),Curs!B45,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B41)),Curs!B41,"")</f>
         <v/>
       </c>
       <c r="B41" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C45)),Curs!C45,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C41)),Curs!C41,"")</f>
         <v/>
       </c>
       <c r="C41" s="10"/>
@@ -13721,11 +13721,11 @@
       <c r="F41" s="10"/>
       <c r="G41" s="10"/>
       <c r="H41" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C45)),ROUND(SUM(C41:G41),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C41)),ROUND(SUM(C41:G41),0),"")</f>
         <v/>
       </c>
       <c r="I41" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C45)),
+        <f>IF(NOT(ISBLANK(Curs!C41)),
 IF(H41=0,"n/p",
 IF(AND(H41&gt;=$J$3,H41&lt;=$K$3),$L$3,
 IF(AND(H41&gt;=$J$4,H41&lt;=$K$4),$L$4,
@@ -13742,11 +13742,11 @@
     </row>
     <row r="42" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A42" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B46)),Curs!B46,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B42)),Curs!B42,"")</f>
         <v/>
       </c>
       <c r="B42" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C46)),Curs!C46,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C42)),Curs!C42,"")</f>
         <v/>
       </c>
       <c r="C42" s="10"/>
@@ -13755,11 +13755,11 @@
       <c r="F42" s="10"/>
       <c r="G42" s="10"/>
       <c r="H42" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C46)),ROUND(SUM(C42:G42),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C42)),ROUND(SUM(C42:G42),0),"")</f>
         <v/>
       </c>
       <c r="I42" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C46)),
+        <f>IF(NOT(ISBLANK(Curs!C42)),
 IF(H42=0,"n/p",
 IF(AND(H42&gt;=$J$3,H42&lt;=$K$3),$L$3,
 IF(AND(H42&gt;=$J$4,H42&lt;=$K$4),$L$4,
@@ -13776,11 +13776,11 @@
     </row>
     <row r="43" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A43" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B47)),Curs!B47,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B43)),Curs!B43,"")</f>
         <v/>
       </c>
       <c r="B43" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C47)),Curs!C47,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C43)),Curs!C43,"")</f>
         <v/>
       </c>
       <c r="C43" s="10"/>
@@ -13789,11 +13789,11 @@
       <c r="F43" s="10"/>
       <c r="G43" s="10"/>
       <c r="H43" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C47)),ROUND(SUM(C43:G43),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C43)),ROUND(SUM(C43:G43),0),"")</f>
         <v/>
       </c>
       <c r="I43" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C47)),
+        <f>IF(NOT(ISBLANK(Curs!C43)),
 IF(H43=0,"n/p",
 IF(AND(H43&gt;=$J$3,H43&lt;=$K$3),$L$3,
 IF(AND(H43&gt;=$J$4,H43&lt;=$K$4),$L$4,
@@ -13810,11 +13810,11 @@
     </row>
     <row r="44" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A44" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B48)),Curs!B48,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B44)),Curs!B44,"")</f>
         <v/>
       </c>
       <c r="B44" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C48)),Curs!C48,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C44)),Curs!C44,"")</f>
         <v/>
       </c>
       <c r="C44" s="10"/>
@@ -13823,11 +13823,11 @@
       <c r="F44" s="10"/>
       <c r="G44" s="10"/>
       <c r="H44" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C48)),ROUND(SUM(C44:G44),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C44)),ROUND(SUM(C44:G44),0),"")</f>
         <v/>
       </c>
       <c r="I44" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C48)),
+        <f>IF(NOT(ISBLANK(Curs!C44)),
 IF(H44=0,"n/p",
 IF(AND(H44&gt;=$J$3,H44&lt;=$K$3),$L$3,
 IF(AND(H44&gt;=$J$4,H44&lt;=$K$4),$L$4,
@@ -13844,11 +13844,11 @@
     </row>
     <row r="45" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A45" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B49)),Curs!B49,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B45)),Curs!B45,"")</f>
         <v/>
       </c>
       <c r="B45" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C49)),Curs!C49,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C45)),Curs!C45,"")</f>
         <v/>
       </c>
       <c r="C45" s="10"/>
@@ -13857,11 +13857,11 @@
       <c r="F45" s="10"/>
       <c r="G45" s="10"/>
       <c r="H45" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C49)),ROUND(SUM(C45:G45),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C45)),ROUND(SUM(C45:G45),0),"")</f>
         <v/>
       </c>
       <c r="I45" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C49)),
+        <f>IF(NOT(ISBLANK(Curs!C45)),
 IF(H45=0,"n/p",
 IF(AND(H45&gt;=$J$3,H45&lt;=$K$3),$L$3,
 IF(AND(H45&gt;=$J$4,H45&lt;=$K$4),$L$4,
@@ -13878,11 +13878,11 @@
     </row>
     <row r="46" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A46" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B50)),Curs!B50,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B46)),Curs!B46,"")</f>
         <v/>
       </c>
       <c r="B46" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C50)),Curs!C50,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C46)),Curs!C46,"")</f>
         <v/>
       </c>
       <c r="C46" s="10"/>
@@ -13891,11 +13891,11 @@
       <c r="F46" s="10"/>
       <c r="G46" s="10"/>
       <c r="H46" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C50)),ROUND(SUM(C46:G46),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C46)),ROUND(SUM(C46:G46),0),"")</f>
         <v/>
       </c>
       <c r="I46" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C50)),
+        <f>IF(NOT(ISBLANK(Curs!C46)),
 IF(H46=0,"n/p",
 IF(AND(H46&gt;=$J$3,H46&lt;=$K$3),$L$3,
 IF(AND(H46&gt;=$J$4,H46&lt;=$K$4),$L$4,
@@ -13912,11 +13912,11 @@
     </row>
     <row r="47" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A47" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B51)),Curs!B51,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B47)),Curs!B47,"")</f>
         <v/>
       </c>
       <c r="B47" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C51)),Curs!C51,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C47)),Curs!C47,"")</f>
         <v/>
       </c>
       <c r="C47" s="10"/>
@@ -13925,11 +13925,11 @@
       <c r="F47" s="10"/>
       <c r="G47" s="10"/>
       <c r="H47" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C51)),ROUND(SUM(C47:G47),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C47)),ROUND(SUM(C47:G47),0),"")</f>
         <v/>
       </c>
       <c r="I47" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C51)),
+        <f>IF(NOT(ISBLANK(Curs!C47)),
 IF(H47=0,"n/p",
 IF(AND(H47&gt;=$J$3,H47&lt;=$K$3),$L$3,
 IF(AND(H47&gt;=$J$4,H47&lt;=$K$4),$L$4,
@@ -13946,11 +13946,11 @@
     </row>
     <row r="48" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A48" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B52)),Curs!B52,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B48)),Curs!B48,"")</f>
         <v/>
       </c>
       <c r="B48" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C52)),Curs!C52,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C48)),Curs!C48,"")</f>
         <v/>
       </c>
       <c r="C48" s="10"/>
@@ -13959,11 +13959,11 @@
       <c r="F48" s="10"/>
       <c r="G48" s="10"/>
       <c r="H48" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C52)),ROUND(SUM(C48:G48),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C48)),ROUND(SUM(C48:G48),0),"")</f>
         <v/>
       </c>
       <c r="I48" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C52)),
+        <f>IF(NOT(ISBLANK(Curs!C48)),
 IF(H48=0,"n/p",
 IF(AND(H48&gt;=$J$3,H48&lt;=$K$3),$L$3,
 IF(AND(H48&gt;=$J$4,H48&lt;=$K$4),$L$4,
@@ -13980,11 +13980,11 @@
     </row>
     <row r="49" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A49" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B53)),Curs!B53,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B49)),Curs!B49,"")</f>
         <v/>
       </c>
       <c r="B49" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C53)),Curs!C53,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C49)),Curs!C49,"")</f>
         <v/>
       </c>
       <c r="C49" s="10"/>
@@ -13993,11 +13993,11 @@
       <c r="F49" s="10"/>
       <c r="G49" s="10"/>
       <c r="H49" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C53)),ROUND(SUM(C49:G49),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C49)),ROUND(SUM(C49:G49),0),"")</f>
         <v/>
       </c>
       <c r="I49" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C53)),
+        <f>IF(NOT(ISBLANK(Curs!C49)),
 IF(H49=0,"n/p",
 IF(AND(H49&gt;=$J$3,H49&lt;=$K$3),$L$3,
 IF(AND(H49&gt;=$J$4,H49&lt;=$K$4),$L$4,
@@ -14014,11 +14014,11 @@
     </row>
     <row r="50" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A50" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B54)),Curs!B54,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B50)),Curs!B50,"")</f>
         <v/>
       </c>
       <c r="B50" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C54)),Curs!C54,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C50)),Curs!C50,"")</f>
         <v/>
       </c>
       <c r="C50" s="10"/>
@@ -14027,11 +14027,11 @@
       <c r="F50" s="10"/>
       <c r="G50" s="10"/>
       <c r="H50" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C54)),ROUND(SUM(C50:G50),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C50)),ROUND(SUM(C50:G50),0),"")</f>
         <v/>
       </c>
       <c r="I50" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C54)),
+        <f>IF(NOT(ISBLANK(Curs!C50)),
 IF(H50=0,"n/p",
 IF(AND(H50&gt;=$J$3,H50&lt;=$K$3),$L$3,
 IF(AND(H50&gt;=$J$4,H50&lt;=$K$4),$L$4,
@@ -14048,11 +14048,11 @@
     </row>
     <row r="51" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A51" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B55)),Curs!B55,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B51)),Curs!B51,"")</f>
         <v/>
       </c>
       <c r="B51" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C55)),Curs!C55,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C51)),Curs!C51,"")</f>
         <v/>
       </c>
       <c r="C51" s="10"/>
@@ -14061,11 +14061,11 @@
       <c r="F51" s="10"/>
       <c r="G51" s="10"/>
       <c r="H51" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C55)),ROUND(SUM(C51:G51),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C51)),ROUND(SUM(C51:G51),0),"")</f>
         <v/>
       </c>
       <c r="I51" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C55)),
+        <f>IF(NOT(ISBLANK(Curs!C51)),
 IF(H51=0,"n/p",
 IF(AND(H51&gt;=$J$3,H51&lt;=$K$3),$L$3,
 IF(AND(H51&gt;=$J$4,H51&lt;=$K$4),$L$4,
@@ -14082,11 +14082,11 @@
     </row>
     <row r="52" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A52" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B56)),Curs!B56,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B52)),Curs!B52,"")</f>
         <v/>
       </c>
       <c r="B52" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C56)),Curs!C56,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C52)),Curs!C52,"")</f>
         <v/>
       </c>
       <c r="C52" s="10"/>
@@ -14095,11 +14095,11 @@
       <c r="F52" s="10"/>
       <c r="G52" s="10"/>
       <c r="H52" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C56)),ROUND(SUM(C52:G52),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C52)),ROUND(SUM(C52:G52),0),"")</f>
         <v/>
       </c>
       <c r="I52" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C56)),
+        <f>IF(NOT(ISBLANK(Curs!C52)),
 IF(H52=0,"n/p",
 IF(AND(H52&gt;=$J$3,H52&lt;=$K$3),$L$3,
 IF(AND(H52&gt;=$J$4,H52&lt;=$K$4),$L$4,
@@ -14116,11 +14116,11 @@
     </row>
     <row r="53" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A53" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B57)),Curs!B57,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B53)),Curs!B53,"")</f>
         <v/>
       </c>
       <c r="B53" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C57)),Curs!C57,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C53)),Curs!C53,"")</f>
         <v/>
       </c>
       <c r="C53" s="10"/>
@@ -14129,11 +14129,11 @@
       <c r="F53" s="10"/>
       <c r="G53" s="10"/>
       <c r="H53" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C57)),ROUND(SUM(C53:G53),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C53)),ROUND(SUM(C53:G53),0),"")</f>
         <v/>
       </c>
       <c r="I53" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C57)),
+        <f>IF(NOT(ISBLANK(Curs!C53)),
 IF(H53=0,"n/p",
 IF(AND(H53&gt;=$J$3,H53&lt;=$K$3),$L$3,
 IF(AND(H53&gt;=$J$4,H53&lt;=$K$4),$L$4,
@@ -14150,11 +14150,11 @@
     </row>
     <row r="54" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A54" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B58)),Curs!B58,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B54)),Curs!B54,"")</f>
         <v/>
       </c>
       <c r="B54" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C58)),Curs!C58,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C54)),Curs!C54,"")</f>
         <v/>
       </c>
       <c r="C54" s="10"/>
@@ -14163,11 +14163,11 @@
       <c r="F54" s="10"/>
       <c r="G54" s="10"/>
       <c r="H54" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C58)),ROUND(SUM(C54:G54),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C54)),ROUND(SUM(C54:G54),0),"")</f>
         <v/>
       </c>
       <c r="I54" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C58)),
+        <f>IF(NOT(ISBLANK(Curs!C54)),
 IF(H54=0,"n/p",
 IF(AND(H54&gt;=$J$3,H54&lt;=$K$3),$L$3,
 IF(AND(H54&gt;=$J$4,H54&lt;=$K$4),$L$4,
@@ -14184,11 +14184,11 @@
     </row>
     <row r="55" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A55" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B59)),Curs!B59,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B55)),Curs!B55,"")</f>
         <v/>
       </c>
       <c r="B55" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C59)),Curs!C59,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C55)),Curs!C55,"")</f>
         <v/>
       </c>
       <c r="C55" s="10"/>
@@ -14197,11 +14197,11 @@
       <c r="F55" s="10"/>
       <c r="G55" s="10"/>
       <c r="H55" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C59)),ROUND(SUM(C55:G55),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C55)),ROUND(SUM(C55:G55),0),"")</f>
         <v/>
       </c>
       <c r="I55" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C59)),
+        <f>IF(NOT(ISBLANK(Curs!C55)),
 IF(H55=0,"n/p",
 IF(AND(H55&gt;=$J$3,H55&lt;=$K$3),$L$3,
 IF(AND(H55&gt;=$J$4,H55&lt;=$K$4),$L$4,
@@ -14218,11 +14218,11 @@
     </row>
     <row r="56" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A56" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B60)),Curs!B60,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B56)),Curs!B56,"")</f>
         <v/>
       </c>
       <c r="B56" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C60)),Curs!C60,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C56)),Curs!C56,"")</f>
         <v/>
       </c>
       <c r="C56" s="10"/>
@@ -14231,11 +14231,11 @@
       <c r="F56" s="10"/>
       <c r="G56" s="10"/>
       <c r="H56" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C60)),ROUND(SUM(C56:G56),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C56)),ROUND(SUM(C56:G56),0),"")</f>
         <v/>
       </c>
       <c r="I56" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C60)),
+        <f>IF(NOT(ISBLANK(Curs!C56)),
 IF(H56=0,"n/p",
 IF(AND(H56&gt;=$J$3,H56&lt;=$K$3),$L$3,
 IF(AND(H56&gt;=$J$4,H56&lt;=$K$4),$L$4,
@@ -14252,11 +14252,11 @@
     </row>
     <row r="57" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A57" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B61)),Curs!B61,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B57)),Curs!B57,"")</f>
         <v/>
       </c>
       <c r="B57" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C61)),Curs!C61,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C57)),Curs!C57,"")</f>
         <v/>
       </c>
       <c r="C57" s="10"/>
@@ -14265,11 +14265,11 @@
       <c r="F57" s="10"/>
       <c r="G57" s="10"/>
       <c r="H57" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C61)),ROUND(SUM(C57:G57),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C57)),ROUND(SUM(C57:G57),0),"")</f>
         <v/>
       </c>
       <c r="I57" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C61)),
+        <f>IF(NOT(ISBLANK(Curs!C57)),
 IF(H57=0,"n/p",
 IF(AND(H57&gt;=$J$3,H57&lt;=$K$3),$L$3,
 IF(AND(H57&gt;=$J$4,H57&lt;=$K$4),$L$4,
@@ -14286,11 +14286,11 @@
     </row>
     <row r="58" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A58" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B62)),Curs!B62,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B58)),Curs!B58,"")</f>
         <v/>
       </c>
       <c r="B58" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C62)),Curs!C62,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C58)),Curs!C58,"")</f>
         <v/>
       </c>
       <c r="C58" s="10"/>
@@ -14299,11 +14299,11 @@
       <c r="F58" s="10"/>
       <c r="G58" s="10"/>
       <c r="H58" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C62)),ROUND(SUM(C58:G58),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C58)),ROUND(SUM(C58:G58),0),"")</f>
         <v/>
       </c>
       <c r="I58" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C62)),
+        <f>IF(NOT(ISBLANK(Curs!C58)),
 IF(H58=0,"n/p",
 IF(AND(H58&gt;=$J$3,H58&lt;=$K$3),$L$3,
 IF(AND(H58&gt;=$J$4,H58&lt;=$K$4),$L$4,
@@ -14320,11 +14320,11 @@
     </row>
     <row r="59" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A59" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B63)),Curs!B63,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B59)),Curs!B59,"")</f>
         <v/>
       </c>
       <c r="B59" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C63)),Curs!C63,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C59)),Curs!C59,"")</f>
         <v/>
       </c>
       <c r="C59" s="10"/>
@@ -14333,11 +14333,11 @@
       <c r="F59" s="10"/>
       <c r="G59" s="10"/>
       <c r="H59" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C63)),ROUND(SUM(C59:G59),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C59)),ROUND(SUM(C59:G59),0),"")</f>
         <v/>
       </c>
       <c r="I59" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C63)),
+        <f>IF(NOT(ISBLANK(Curs!C59)),
 IF(H59=0,"n/p",
 IF(AND(H59&gt;=$J$3,H59&lt;=$K$3),$L$3,
 IF(AND(H59&gt;=$J$4,H59&lt;=$K$4),$L$4,
@@ -14354,11 +14354,11 @@
     </row>
     <row r="60" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A60" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B64)),Curs!B64,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B60)),Curs!B60,"")</f>
         <v/>
       </c>
       <c r="B60" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C64)),Curs!C64,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C60)),Curs!C60,"")</f>
         <v/>
       </c>
       <c r="C60" s="10"/>
@@ -14367,11 +14367,11 @@
       <c r="F60" s="10"/>
       <c r="G60" s="10"/>
       <c r="H60" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C64)),ROUND(SUM(C60:G60),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C60)),ROUND(SUM(C60:G60),0),"")</f>
         <v/>
       </c>
       <c r="I60" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C64)),
+        <f>IF(NOT(ISBLANK(Curs!C60)),
 IF(H60=0,"n/p",
 IF(AND(H60&gt;=$J$3,H60&lt;=$K$3),$L$3,
 IF(AND(H60&gt;=$J$4,H60&lt;=$K$4),$L$4,
@@ -14388,11 +14388,11 @@
     </row>
     <row r="61" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A61" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B65)),Curs!B65,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B61)),Curs!B61,"")</f>
         <v/>
       </c>
       <c r="B61" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C65)),Curs!C65,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C61)),Curs!C61,"")</f>
         <v/>
       </c>
       <c r="C61" s="10"/>
@@ -14401,11 +14401,11 @@
       <c r="F61" s="10"/>
       <c r="G61" s="10"/>
       <c r="H61" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C65)),ROUND(SUM(C61:G61),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C61)),ROUND(SUM(C61:G61),0),"")</f>
         <v/>
       </c>
       <c r="I61" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C65)),
+        <f>IF(NOT(ISBLANK(Curs!C61)),
 IF(H61=0,"n/p",
 IF(AND(H61&gt;=$J$3,H61&lt;=$K$3),$L$3,
 IF(AND(H61&gt;=$J$4,H61&lt;=$K$4),$L$4,
@@ -14422,11 +14422,11 @@
     </row>
     <row r="62" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A62" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B66)),Curs!B66,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B62)),Curs!B62,"")</f>
         <v/>
       </c>
       <c r="B62" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C66)),Curs!C66,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C62)),Curs!C62,"")</f>
         <v/>
       </c>
       <c r="C62" s="10"/>
@@ -14435,11 +14435,11 @@
       <c r="F62" s="10"/>
       <c r="G62" s="10"/>
       <c r="H62" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C66)),ROUND(SUM(C62:G62),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C62)),ROUND(SUM(C62:G62),0),"")</f>
         <v/>
       </c>
       <c r="I62" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C66)),
+        <f>IF(NOT(ISBLANK(Curs!C62)),
 IF(H62=0,"n/p",
 IF(AND(H62&gt;=$J$3,H62&lt;=$K$3),$L$3,
 IF(AND(H62&gt;=$J$4,H62&lt;=$K$4),$L$4,
@@ -14456,11 +14456,11 @@
     </row>
     <row r="63" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A63" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B67)),Curs!B67,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B63)),Curs!B63,"")</f>
         <v/>
       </c>
       <c r="B63" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C67)),Curs!C67,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C63)),Curs!C63,"")</f>
         <v/>
       </c>
       <c r="C63" s="10"/>
@@ -14469,11 +14469,11 @@
       <c r="F63" s="10"/>
       <c r="G63" s="10"/>
       <c r="H63" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C67)),ROUND(SUM(C63:G63),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C63)),ROUND(SUM(C63:G63),0),"")</f>
         <v/>
       </c>
       <c r="I63" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C67)),
+        <f>IF(NOT(ISBLANK(Curs!C63)),
 IF(H63=0,"n/p",
 IF(AND(H63&gt;=$J$3,H63&lt;=$K$3),$L$3,
 IF(AND(H63&gt;=$J$4,H63&lt;=$K$4),$L$4,
@@ -14490,11 +14490,11 @@
     </row>
     <row r="64" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A64" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B68)),Curs!B68,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B64)),Curs!B64,"")</f>
         <v/>
       </c>
       <c r="B64" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C68)),Curs!C68,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C64)),Curs!C64,"")</f>
         <v/>
       </c>
       <c r="C64" s="10"/>
@@ -14503,11 +14503,11 @@
       <c r="F64" s="10"/>
       <c r="G64" s="10"/>
       <c r="H64" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C68)),ROUND(SUM(C64:G64),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C64)),ROUND(SUM(C64:G64),0),"")</f>
         <v/>
       </c>
       <c r="I64" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C68)),
+        <f>IF(NOT(ISBLANK(Curs!C64)),
 IF(H64=0,"n/p",
 IF(AND(H64&gt;=$J$3,H64&lt;=$K$3),$L$3,
 IF(AND(H64&gt;=$J$4,H64&lt;=$K$4),$L$4,
@@ -14524,11 +14524,11 @@
     </row>
     <row r="65" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A65" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B69)),Curs!B69,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B65)),Curs!B65,"")</f>
         <v/>
       </c>
       <c r="B65" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C69)),Curs!C69,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C65)),Curs!C65,"")</f>
         <v/>
       </c>
       <c r="C65" s="10"/>
@@ -14537,11 +14537,11 @@
       <c r="F65" s="10"/>
       <c r="G65" s="10"/>
       <c r="H65" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C69)),ROUND(SUM(C65:G65),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C65)),ROUND(SUM(C65:G65),0),"")</f>
         <v/>
       </c>
       <c r="I65" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C69)),
+        <f>IF(NOT(ISBLANK(Curs!C65)),
 IF(H65=0,"n/p",
 IF(AND(H65&gt;=$J$3,H65&lt;=$K$3),$L$3,
 IF(AND(H65&gt;=$J$4,H65&lt;=$K$4),$L$4,
@@ -14558,11 +14558,11 @@
     </row>
     <row r="66" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A66" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B70)),Curs!B70,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B66)),Curs!B66,"")</f>
         <v/>
       </c>
       <c r="B66" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C70)),Curs!C70,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C66)),Curs!C66,"")</f>
         <v/>
       </c>
       <c r="C66" s="10"/>
@@ -14571,11 +14571,11 @@
       <c r="F66" s="10"/>
       <c r="G66" s="10"/>
       <c r="H66" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C70)),ROUND(SUM(C66:G66),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C66)),ROUND(SUM(C66:G66),0),"")</f>
         <v/>
       </c>
       <c r="I66" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C70)),
+        <f>IF(NOT(ISBLANK(Curs!C66)),
 IF(H66=0,"n/p",
 IF(AND(H66&gt;=$J$3,H66&lt;=$K$3),$L$3,
 IF(AND(H66&gt;=$J$4,H66&lt;=$K$4),$L$4,
@@ -14592,11 +14592,11 @@
     </row>
     <row r="67" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A67" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B71)),Curs!B71,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B67)),Curs!B67,"")</f>
         <v/>
       </c>
       <c r="B67" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C71)),Curs!C71,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C67)),Curs!C67,"")</f>
         <v/>
       </c>
       <c r="C67" s="10"/>
@@ -14605,11 +14605,11 @@
       <c r="F67" s="10"/>
       <c r="G67" s="10"/>
       <c r="H67" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C71)),ROUND(SUM(C67:G67),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C67)),ROUND(SUM(C67:G67),0),"")</f>
         <v/>
       </c>
       <c r="I67" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C71)),
+        <f>IF(NOT(ISBLANK(Curs!C67)),
 IF(H67=0,"n/p",
 IF(AND(H67&gt;=$J$3,H67&lt;=$K$3),$L$3,
 IF(AND(H67&gt;=$J$4,H67&lt;=$K$4),$L$4,
@@ -14626,11 +14626,11 @@
     </row>
     <row r="68" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A68" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B72)),Curs!B72,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B68)),Curs!B68,"")</f>
         <v/>
       </c>
       <c r="B68" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C72)),Curs!C72,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C68)),Curs!C68,"")</f>
         <v/>
       </c>
       <c r="C68" s="10"/>
@@ -14639,11 +14639,11 @@
       <c r="F68" s="10"/>
       <c r="G68" s="10"/>
       <c r="H68" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C72)),ROUND(SUM(C68:G68),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C68)),ROUND(SUM(C68:G68),0),"")</f>
         <v/>
       </c>
       <c r="I68" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C72)),
+        <f>IF(NOT(ISBLANK(Curs!C68)),
 IF(H68=0,"n/p",
 IF(AND(H68&gt;=$J$3,H68&lt;=$K$3),$L$3,
 IF(AND(H68&gt;=$J$4,H68&lt;=$K$4),$L$4,
@@ -14660,11 +14660,11 @@
     </row>
     <row r="69" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A69" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B73)),Curs!B73,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B69)),Curs!B69,"")</f>
         <v/>
       </c>
       <c r="B69" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C73)),Curs!C73,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C69)),Curs!C69,"")</f>
         <v/>
       </c>
       <c r="C69" s="10"/>
@@ -14673,11 +14673,11 @@
       <c r="F69" s="10"/>
       <c r="G69" s="10"/>
       <c r="H69" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C73)),ROUND(SUM(C69:G69),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C69)),ROUND(SUM(C69:G69),0),"")</f>
         <v/>
       </c>
       <c r="I69" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C73)),
+        <f>IF(NOT(ISBLANK(Curs!C69)),
 IF(H69=0,"n/p",
 IF(AND(H69&gt;=$J$3,H69&lt;=$K$3),$L$3,
 IF(AND(H69&gt;=$J$4,H69&lt;=$K$4),$L$4,
@@ -14694,11 +14694,11 @@
     </row>
     <row r="70" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A70" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B74)),Curs!B74,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B70)),Curs!B70,"")</f>
         <v/>
       </c>
       <c r="B70" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C74)),Curs!C74,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C70)),Curs!C70,"")</f>
         <v/>
       </c>
       <c r="C70" s="10"/>
@@ -14707,11 +14707,11 @@
       <c r="F70" s="10"/>
       <c r="G70" s="10"/>
       <c r="H70" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C74)),ROUND(SUM(C70:G70),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C70)),ROUND(SUM(C70:G70),0),"")</f>
         <v/>
       </c>
       <c r="I70" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C74)),
+        <f>IF(NOT(ISBLANK(Curs!C70)),
 IF(H70=0,"n/p",
 IF(AND(H70&gt;=$J$3,H70&lt;=$K$3),$L$3,
 IF(AND(H70&gt;=$J$4,H70&lt;=$K$4),$L$4,
@@ -14728,11 +14728,11 @@
     </row>
     <row r="71" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A71" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B75)),Curs!B75,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B71)),Curs!B71,"")</f>
         <v/>
       </c>
       <c r="B71" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C75)),Curs!C75,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C71)),Curs!C71,"")</f>
         <v/>
       </c>
       <c r="C71" s="10"/>
@@ -14741,11 +14741,11 @@
       <c r="F71" s="10"/>
       <c r="G71" s="10"/>
       <c r="H71" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C75)),ROUND(SUM(C71:G71),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C71)),ROUND(SUM(C71:G71),0),"")</f>
         <v/>
       </c>
       <c r="I71" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C75)),
+        <f>IF(NOT(ISBLANK(Curs!C71)),
 IF(H71=0,"n/p",
 IF(AND(H71&gt;=$J$3,H71&lt;=$K$3),$L$3,
 IF(AND(H71&gt;=$J$4,H71&lt;=$K$4),$L$4,
@@ -14762,11 +14762,11 @@
     </row>
     <row r="72" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A72" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B76)),Curs!B76,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B72)),Curs!B72,"")</f>
         <v/>
       </c>
       <c r="B72" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C76)),Curs!C76,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C72)),Curs!C72,"")</f>
         <v/>
       </c>
       <c r="C72" s="10"/>
@@ -14775,11 +14775,11 @@
       <c r="F72" s="10"/>
       <c r="G72" s="10"/>
       <c r="H72" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C76)),ROUND(SUM(C72:G72),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C72)),ROUND(SUM(C72:G72),0),"")</f>
         <v/>
       </c>
       <c r="I72" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C76)),
+        <f>IF(NOT(ISBLANK(Curs!C72)),
 IF(H72=0,"n/p",
 IF(AND(H72&gt;=$J$3,H72&lt;=$K$3),$L$3,
 IF(AND(H72&gt;=$J$4,H72&lt;=$K$4),$L$4,
@@ -14796,11 +14796,11 @@
     </row>
     <row r="73" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A73" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B77)),Curs!B77,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B73)),Curs!B73,"")</f>
         <v/>
       </c>
       <c r="B73" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C77)),Curs!C77,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C73)),Curs!C73,"")</f>
         <v/>
       </c>
       <c r="C73" s="10"/>
@@ -14809,11 +14809,11 @@
       <c r="F73" s="10"/>
       <c r="G73" s="10"/>
       <c r="H73" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C77)),ROUND(SUM(C73:G73),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C73)),ROUND(SUM(C73:G73),0),"")</f>
         <v/>
       </c>
       <c r="I73" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C77)),
+        <f>IF(NOT(ISBLANK(Curs!C73)),
 IF(H73=0,"n/p",
 IF(AND(H73&gt;=$J$3,H73&lt;=$K$3),$L$3,
 IF(AND(H73&gt;=$J$4,H73&lt;=$K$4),$L$4,
@@ -14830,11 +14830,11 @@
     </row>
     <row r="74" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A74" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B78)),Curs!B78,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B74)),Curs!B74,"")</f>
         <v/>
       </c>
       <c r="B74" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C78)),Curs!C78,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C74)),Curs!C74,"")</f>
         <v/>
       </c>
       <c r="C74" s="10"/>
@@ -14843,11 +14843,11 @@
       <c r="F74" s="10"/>
       <c r="G74" s="10"/>
       <c r="H74" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C78)),ROUND(SUM(C74:G74),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C74)),ROUND(SUM(C74:G74),0),"")</f>
         <v/>
       </c>
       <c r="I74" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C78)),
+        <f>IF(NOT(ISBLANK(Curs!C74)),
 IF(H74=0,"n/p",
 IF(AND(H74&gt;=$J$3,H74&lt;=$K$3),$L$3,
 IF(AND(H74&gt;=$J$4,H74&lt;=$K$4),$L$4,
@@ -14864,11 +14864,11 @@
     </row>
     <row r="75" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A75" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B79)),Curs!B79,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B75)),Curs!B75,"")</f>
         <v/>
       </c>
       <c r="B75" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C79)),Curs!C79,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C75)),Curs!C75,"")</f>
         <v/>
       </c>
       <c r="C75" s="10"/>
@@ -14877,11 +14877,11 @@
       <c r="F75" s="10"/>
       <c r="G75" s="10"/>
       <c r="H75" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C79)),ROUND(SUM(C75:G75),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C75)),ROUND(SUM(C75:G75),0),"")</f>
         <v/>
       </c>
       <c r="I75" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C79)),
+        <f>IF(NOT(ISBLANK(Curs!C75)),
 IF(H75=0,"n/p",
 IF(AND(H75&gt;=$J$3,H75&lt;=$K$3),$L$3,
 IF(AND(H75&gt;=$J$4,H75&lt;=$K$4),$L$4,
@@ -14898,11 +14898,11 @@
     </row>
     <row r="76" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A76" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B80)),Curs!B80,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B76)),Curs!B76,"")</f>
         <v/>
       </c>
       <c r="B76" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C80)),Curs!C80,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C76)),Curs!C76,"")</f>
         <v/>
       </c>
       <c r="C76" s="10"/>
@@ -14911,11 +14911,11 @@
       <c r="F76" s="10"/>
       <c r="G76" s="10"/>
       <c r="H76" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C80)),ROUND(SUM(C76:G76),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C76)),ROUND(SUM(C76:G76),0),"")</f>
         <v/>
       </c>
       <c r="I76" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C80)),
+        <f>IF(NOT(ISBLANK(Curs!C76)),
 IF(H76=0,"n/p",
 IF(AND(H76&gt;=$J$3,H76&lt;=$K$3),$L$3,
 IF(AND(H76&gt;=$J$4,H76&lt;=$K$4),$L$4,
@@ -14932,11 +14932,11 @@
     </row>
     <row r="77" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A77" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B81)),Curs!B81,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B77)),Curs!B77,"")</f>
         <v/>
       </c>
       <c r="B77" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C81)),Curs!C81,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C77)),Curs!C77,"")</f>
         <v/>
       </c>
       <c r="C77" s="10"/>
@@ -14945,11 +14945,11 @@
       <c r="F77" s="10"/>
       <c r="G77" s="10"/>
       <c r="H77" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C81)),ROUND(SUM(C77:G77),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C77)),ROUND(SUM(C77:G77),0),"")</f>
         <v/>
       </c>
       <c r="I77" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C81)),
+        <f>IF(NOT(ISBLANK(Curs!C77)),
 IF(H77=0,"n/p",
 IF(AND(H77&gt;=$J$3,H77&lt;=$K$3),$L$3,
 IF(AND(H77&gt;=$J$4,H77&lt;=$K$4),$L$4,
@@ -14966,11 +14966,11 @@
     </row>
     <row r="78" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A78" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B82)),Curs!B82,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B78)),Curs!B78,"")</f>
         <v/>
       </c>
       <c r="B78" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C82)),Curs!C82,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C78)),Curs!C78,"")</f>
         <v/>
       </c>
       <c r="C78" s="10"/>
@@ -14979,11 +14979,11 @@
       <c r="F78" s="10"/>
       <c r="G78" s="10"/>
       <c r="H78" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C82)),ROUND(SUM(C78:G78),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C78)),ROUND(SUM(C78:G78),0),"")</f>
         <v/>
       </c>
       <c r="I78" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C82)),
+        <f>IF(NOT(ISBLANK(Curs!C78)),
 IF(H78=0,"n/p",
 IF(AND(H78&gt;=$J$3,H78&lt;=$K$3),$L$3,
 IF(AND(H78&gt;=$J$4,H78&lt;=$K$4),$L$4,
@@ -15000,11 +15000,11 @@
     </row>
     <row r="79" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A79" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B83)),Curs!B83,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B79)),Curs!B79,"")</f>
         <v/>
       </c>
       <c r="B79" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C83)),Curs!C83,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C79)),Curs!C79,"")</f>
         <v/>
       </c>
       <c r="C79" s="10"/>
@@ -15013,11 +15013,11 @@
       <c r="F79" s="10"/>
       <c r="G79" s="10"/>
       <c r="H79" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C83)),ROUND(SUM(C79:G79),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C79)),ROUND(SUM(C79:G79),0),"")</f>
         <v/>
       </c>
       <c r="I79" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C83)),
+        <f>IF(NOT(ISBLANK(Curs!C79)),
 IF(H79=0,"n/p",
 IF(AND(H79&gt;=$J$3,H79&lt;=$K$3),$L$3,
 IF(AND(H79&gt;=$J$4,H79&lt;=$K$4),$L$4,
@@ -15034,11 +15034,11 @@
     </row>
     <row r="80" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A80" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B84)),Curs!B84,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B80)),Curs!B80,"")</f>
         <v/>
       </c>
       <c r="B80" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C84)),Curs!C84,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C80)),Curs!C80,"")</f>
         <v/>
       </c>
       <c r="C80" s="10"/>
@@ -15047,11 +15047,11 @@
       <c r="F80" s="10"/>
       <c r="G80" s="10"/>
       <c r="H80" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C84)),ROUND(SUM(C80:G80),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C80)),ROUND(SUM(C80:G80),0),"")</f>
         <v/>
       </c>
       <c r="I80" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C84)),
+        <f>IF(NOT(ISBLANK(Curs!C80)),
 IF(H80=0,"n/p",
 IF(AND(H80&gt;=$J$3,H80&lt;=$K$3),$L$3,
 IF(AND(H80&gt;=$J$4,H80&lt;=$K$4),$L$4,
@@ -15068,11 +15068,11 @@
     </row>
     <row r="81" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A81" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B85)),Curs!B85,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B81)),Curs!B81,"")</f>
         <v/>
       </c>
       <c r="B81" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C85)),Curs!C85,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C81)),Curs!C81,"")</f>
         <v/>
       </c>
       <c r="C81" s="10"/>
@@ -15081,11 +15081,11 @@
       <c r="F81" s="10"/>
       <c r="G81" s="10"/>
       <c r="H81" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C85)),ROUND(SUM(C81:G81),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C81)),ROUND(SUM(C81:G81),0),"")</f>
         <v/>
       </c>
       <c r="I81" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C85)),
+        <f>IF(NOT(ISBLANK(Curs!C81)),
 IF(H81=0,"n/p",
 IF(AND(H81&gt;=$J$3,H81&lt;=$K$3),$L$3,
 IF(AND(H81&gt;=$J$4,H81&lt;=$K$4),$L$4,
@@ -15102,11 +15102,11 @@
     </row>
     <row r="82" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A82" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B86)),Curs!B86,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B82)),Curs!B82,"")</f>
         <v/>
       </c>
       <c r="B82" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C86)),Curs!C86,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C82)),Curs!C82,"")</f>
         <v/>
       </c>
       <c r="C82" s="10"/>
@@ -15115,11 +15115,11 @@
       <c r="F82" s="10"/>
       <c r="G82" s="10"/>
       <c r="H82" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C86)),ROUND(SUM(C82:G82),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C82)),ROUND(SUM(C82:G82),0),"")</f>
         <v/>
       </c>
       <c r="I82" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C86)),
+        <f>IF(NOT(ISBLANK(Curs!C82)),
 IF(H82=0,"n/p",
 IF(AND(H82&gt;=$J$3,H82&lt;=$K$3),$L$3,
 IF(AND(H82&gt;=$J$4,H82&lt;=$K$4),$L$4,
@@ -15136,11 +15136,11 @@
     </row>
     <row r="83" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A83" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B87)),Curs!B87,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B83)),Curs!B83,"")</f>
         <v/>
       </c>
       <c r="B83" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C87)),Curs!C87,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C83)),Curs!C83,"")</f>
         <v/>
       </c>
       <c r="C83" s="10"/>
@@ -15149,11 +15149,11 @@
       <c r="F83" s="10"/>
       <c r="G83" s="10"/>
       <c r="H83" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C87)),ROUND(SUM(C83:G83),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C83)),ROUND(SUM(C83:G83),0),"")</f>
         <v/>
       </c>
       <c r="I83" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C87)),
+        <f>IF(NOT(ISBLANK(Curs!C83)),
 IF(H83=0,"n/p",
 IF(AND(H83&gt;=$J$3,H83&lt;=$K$3),$L$3,
 IF(AND(H83&gt;=$J$4,H83&lt;=$K$4),$L$4,
@@ -15170,11 +15170,11 @@
     </row>
     <row r="84" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A84" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B88)),Curs!B88,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B84)),Curs!B84,"")</f>
         <v/>
       </c>
       <c r="B84" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C88)),Curs!C88,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C84)),Curs!C84,"")</f>
         <v/>
       </c>
       <c r="C84" s="10"/>
@@ -15183,11 +15183,11 @@
       <c r="F84" s="10"/>
       <c r="G84" s="10"/>
       <c r="H84" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C88)),ROUND(SUM(C84:G84),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C84)),ROUND(SUM(C84:G84),0),"")</f>
         <v/>
       </c>
       <c r="I84" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C88)),
+        <f>IF(NOT(ISBLANK(Curs!C84)),
 IF(H84=0,"n/p",
 IF(AND(H84&gt;=$J$3,H84&lt;=$K$3),$L$3,
 IF(AND(H84&gt;=$J$4,H84&lt;=$K$4),$L$4,
@@ -15204,11 +15204,11 @@
     </row>
     <row r="85" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A85" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B89)),Curs!B89,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B85)),Curs!B85,"")</f>
         <v/>
       </c>
       <c r="B85" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C89)),Curs!C89,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C85)),Curs!C85,"")</f>
         <v/>
       </c>
       <c r="C85" s="10"/>
@@ -15217,11 +15217,11 @@
       <c r="F85" s="10"/>
       <c r="G85" s="10"/>
       <c r="H85" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C89)),ROUND(SUM(C85:G85),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C85)),ROUND(SUM(C85:G85),0),"")</f>
         <v/>
       </c>
       <c r="I85" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C89)),
+        <f>IF(NOT(ISBLANK(Curs!C85)),
 IF(H85=0,"n/p",
 IF(AND(H85&gt;=$J$3,H85&lt;=$K$3),$L$3,
 IF(AND(H85&gt;=$J$4,H85&lt;=$K$4),$L$4,
@@ -15238,11 +15238,11 @@
     </row>
     <row r="86" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A86" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B90)),Curs!B90,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B86)),Curs!B86,"")</f>
         <v/>
       </c>
       <c r="B86" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C90)),Curs!C90,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C86)),Curs!C86,"")</f>
         <v/>
       </c>
       <c r="C86" s="10"/>
@@ -15251,11 +15251,11 @@
       <c r="F86" s="10"/>
       <c r="G86" s="10"/>
       <c r="H86" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C90)),ROUND(SUM(C86:G86),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C86)),ROUND(SUM(C86:G86),0),"")</f>
         <v/>
       </c>
       <c r="I86" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C90)),
+        <f>IF(NOT(ISBLANK(Curs!C86)),
 IF(H86=0,"n/p",
 IF(AND(H86&gt;=$J$3,H86&lt;=$K$3),$L$3,
 IF(AND(H86&gt;=$J$4,H86&lt;=$K$4),$L$4,
@@ -15272,11 +15272,11 @@
     </row>
     <row r="87" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A87" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B91)),Curs!B91,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B87)),Curs!B87,"")</f>
         <v/>
       </c>
       <c r="B87" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C91)),Curs!C91,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C87)),Curs!C87,"")</f>
         <v/>
       </c>
       <c r="C87" s="10"/>
@@ -15285,11 +15285,11 @@
       <c r="F87" s="10"/>
       <c r="G87" s="10"/>
       <c r="H87" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C91)),ROUND(SUM(C87:G87),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C87)),ROUND(SUM(C87:G87),0),"")</f>
         <v/>
       </c>
       <c r="I87" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C91)),
+        <f>IF(NOT(ISBLANK(Curs!C87)),
 IF(H87=0,"n/p",
 IF(AND(H87&gt;=$J$3,H87&lt;=$K$3),$L$3,
 IF(AND(H87&gt;=$J$4,H87&lt;=$K$4),$L$4,
@@ -15306,11 +15306,11 @@
     </row>
     <row r="88" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A88" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B92)),Curs!B92,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B88)),Curs!B88,"")</f>
         <v/>
       </c>
       <c r="B88" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C92)),Curs!C92,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C88)),Curs!C88,"")</f>
         <v/>
       </c>
       <c r="C88" s="10"/>
@@ -15319,11 +15319,11 @@
       <c r="F88" s="10"/>
       <c r="G88" s="10"/>
       <c r="H88" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C92)),ROUND(SUM(C88:G88),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C88)),ROUND(SUM(C88:G88),0),"")</f>
         <v/>
       </c>
       <c r="I88" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C92)),
+        <f>IF(NOT(ISBLANK(Curs!C88)),
 IF(H88=0,"n/p",
 IF(AND(H88&gt;=$J$3,H88&lt;=$K$3),$L$3,
 IF(AND(H88&gt;=$J$4,H88&lt;=$K$4),$L$4,
@@ -15340,11 +15340,11 @@
     </row>
     <row r="89" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A89" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B93)),Curs!B93,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B89)),Curs!B89,"")</f>
         <v/>
       </c>
       <c r="B89" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C93)),Curs!C93,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C89)),Curs!C89,"")</f>
         <v/>
       </c>
       <c r="C89" s="10"/>
@@ -15353,11 +15353,11 @@
       <c r="F89" s="10"/>
       <c r="G89" s="10"/>
       <c r="H89" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C93)),ROUND(SUM(C89:G89),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C89)),ROUND(SUM(C89:G89),0),"")</f>
         <v/>
       </c>
       <c r="I89" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C93)),
+        <f>IF(NOT(ISBLANK(Curs!C89)),
 IF(H89=0,"n/p",
 IF(AND(H89&gt;=$J$3,H89&lt;=$K$3),$L$3,
 IF(AND(H89&gt;=$J$4,H89&lt;=$K$4),$L$4,
@@ -15374,11 +15374,11 @@
     </row>
     <row r="90" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A90" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B94)),Curs!B94,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B90)),Curs!B90,"")</f>
         <v/>
       </c>
       <c r="B90" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C94)),Curs!C94,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C90)),Curs!C90,"")</f>
         <v/>
       </c>
       <c r="C90" s="10"/>
@@ -15387,11 +15387,11 @@
       <c r="F90" s="10"/>
       <c r="G90" s="10"/>
       <c r="H90" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C94)),ROUND(SUM(C90:G90),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C90)),ROUND(SUM(C90:G90),0),"")</f>
         <v/>
       </c>
       <c r="I90" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C94)),
+        <f>IF(NOT(ISBLANK(Curs!C90)),
 IF(H90=0,"n/p",
 IF(AND(H90&gt;=$J$3,H90&lt;=$K$3),$L$3,
 IF(AND(H90&gt;=$J$4,H90&lt;=$K$4),$L$4,
@@ -15408,11 +15408,11 @@
     </row>
     <row r="91" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A91" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B95)),Curs!B95,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B91)),Curs!B91,"")</f>
         <v/>
       </c>
       <c r="B91" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C95)),Curs!C95,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C91)),Curs!C91,"")</f>
         <v/>
       </c>
       <c r="C91" s="10"/>
@@ -15421,11 +15421,11 @@
       <c r="F91" s="10"/>
       <c r="G91" s="10"/>
       <c r="H91" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C95)),ROUND(SUM(C91:G91),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C91)),ROUND(SUM(C91:G91),0),"")</f>
         <v/>
       </c>
       <c r="I91" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C95)),
+        <f>IF(NOT(ISBLANK(Curs!C91)),
 IF(H91=0,"n/p",
 IF(AND(H91&gt;=$J$3,H91&lt;=$K$3),$L$3,
 IF(AND(H91&gt;=$J$4,H91&lt;=$K$4),$L$4,
@@ -15442,11 +15442,11 @@
     </row>
     <row r="92" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A92" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B96)),Curs!B96,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B92)),Curs!B92,"")</f>
         <v/>
       </c>
       <c r="B92" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C96)),Curs!C96,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C92)),Curs!C92,"")</f>
         <v/>
       </c>
       <c r="C92" s="10"/>
@@ -15455,11 +15455,11 @@
       <c r="F92" s="10"/>
       <c r="G92" s="10"/>
       <c r="H92" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C96)),ROUND(SUM(C92:G92),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C92)),ROUND(SUM(C92:G92),0),"")</f>
         <v/>
       </c>
       <c r="I92" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C96)),
+        <f>IF(NOT(ISBLANK(Curs!C92)),
 IF(H92=0,"n/p",
 IF(AND(H92&gt;=$J$3,H92&lt;=$K$3),$L$3,
 IF(AND(H92&gt;=$J$4,H92&lt;=$K$4),$L$4,
@@ -15476,11 +15476,11 @@
     </row>
     <row r="93" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A93" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B97)),Curs!B97,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B93)),Curs!B93,"")</f>
         <v/>
       </c>
       <c r="B93" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C97)),Curs!C97,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C93)),Curs!C93,"")</f>
         <v/>
       </c>
       <c r="C93" s="10"/>
@@ -15489,11 +15489,11 @@
       <c r="F93" s="10"/>
       <c r="G93" s="10"/>
       <c r="H93" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C97)),ROUND(SUM(C93:G93),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C93)),ROUND(SUM(C93:G93),0),"")</f>
         <v/>
       </c>
       <c r="I93" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C97)),
+        <f>IF(NOT(ISBLANK(Curs!C93)),
 IF(H93=0,"n/p",
 IF(AND(H93&gt;=$J$3,H93&lt;=$K$3),$L$3,
 IF(AND(H93&gt;=$J$4,H93&lt;=$K$4),$L$4,
@@ -15510,11 +15510,11 @@
     </row>
     <row r="94" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A94" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B98)),Curs!B98,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B94)),Curs!B94,"")</f>
         <v/>
       </c>
       <c r="B94" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C98)),Curs!C98,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C94)),Curs!C94,"")</f>
         <v/>
       </c>
       <c r="C94" s="10"/>
@@ -15523,11 +15523,11 @@
       <c r="F94" s="10"/>
       <c r="G94" s="10"/>
       <c r="H94" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C98)),ROUND(SUM(C94:G94),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C94)),ROUND(SUM(C94:G94),0),"")</f>
         <v/>
       </c>
       <c r="I94" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C98)),
+        <f>IF(NOT(ISBLANK(Curs!C94)),
 IF(H94=0,"n/p",
 IF(AND(H94&gt;=$J$3,H94&lt;=$K$3),$L$3,
 IF(AND(H94&gt;=$J$4,H94&lt;=$K$4),$L$4,
@@ -15544,11 +15544,11 @@
     </row>
     <row r="95" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A95" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B99)),Curs!B99,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B95)),Curs!B95,"")</f>
         <v/>
       </c>
       <c r="B95" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C99)),Curs!C99,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C95)),Curs!C95,"")</f>
         <v/>
       </c>
       <c r="C95" s="10"/>
@@ -15557,11 +15557,11 @@
       <c r="F95" s="10"/>
       <c r="G95" s="10"/>
       <c r="H95" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C99)),ROUND(SUM(C95:G95),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C95)),ROUND(SUM(C95:G95),0),"")</f>
         <v/>
       </c>
       <c r="I95" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C99)),
+        <f>IF(NOT(ISBLANK(Curs!C95)),
 IF(H95=0,"n/p",
 IF(AND(H95&gt;=$J$3,H95&lt;=$K$3),$L$3,
 IF(AND(H95&gt;=$J$4,H95&lt;=$K$4),$L$4,
@@ -15578,11 +15578,11 @@
     </row>
     <row r="96" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A96" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B100)),Curs!B100,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B96)),Curs!B96,"")</f>
         <v/>
       </c>
       <c r="B96" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C100)),Curs!C100,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C96)),Curs!C96,"")</f>
         <v/>
       </c>
       <c r="C96" s="10"/>
@@ -15591,11 +15591,11 @@
       <c r="F96" s="10"/>
       <c r="G96" s="10"/>
       <c r="H96" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C100)),ROUND(SUM(C96:G96),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C96)),ROUND(SUM(C96:G96),0),"")</f>
         <v/>
       </c>
       <c r="I96" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C100)),
+        <f>IF(NOT(ISBLANK(Curs!C96)),
 IF(H96=0,"n/p",
 IF(AND(H96&gt;=$J$3,H96&lt;=$K$3),$L$3,
 IF(AND(H96&gt;=$J$4,H96&lt;=$K$4),$L$4,
@@ -15612,11 +15612,11 @@
     </row>
     <row r="97" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A97" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B101)),Curs!B101,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B97)),Curs!B97,"")</f>
         <v/>
       </c>
       <c r="B97" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C101)),Curs!C101,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C97)),Curs!C97,"")</f>
         <v/>
       </c>
       <c r="C97" s="10"/>
@@ -15625,11 +15625,11 @@
       <c r="F97" s="10"/>
       <c r="G97" s="10"/>
       <c r="H97" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C101)),ROUND(SUM(C97:G97),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C97)),ROUND(SUM(C97:G97),0),"")</f>
         <v/>
       </c>
       <c r="I97" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C101)),
+        <f>IF(NOT(ISBLANK(Curs!C97)),
 IF(H97=0,"n/p",
 IF(AND(H97&gt;=$J$3,H97&lt;=$K$3),$L$3,
 IF(AND(H97&gt;=$J$4,H97&lt;=$K$4),$L$4,
@@ -15646,11 +15646,11 @@
     </row>
     <row r="98" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A98" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B102)),Curs!B102,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B98)),Curs!B98,"")</f>
         <v/>
       </c>
       <c r="B98" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C102)),Curs!C102,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C98)),Curs!C98,"")</f>
         <v/>
       </c>
       <c r="C98" s="10"/>
@@ -15659,11 +15659,11 @@
       <c r="F98" s="10"/>
       <c r="G98" s="10"/>
       <c r="H98" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C102)),ROUND(SUM(C98:G98),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C98)),ROUND(SUM(C98:G98),0),"")</f>
         <v/>
       </c>
       <c r="I98" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C102)),
+        <f>IF(NOT(ISBLANK(Curs!C98)),
 IF(H98=0,"n/p",
 IF(AND(H98&gt;=$J$3,H98&lt;=$K$3),$L$3,
 IF(AND(H98&gt;=$J$4,H98&lt;=$K$4),$L$4,
@@ -15680,11 +15680,11 @@
     </row>
     <row r="99" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A99" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B103)),Curs!B103,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B99)),Curs!B99,"")</f>
         <v/>
       </c>
       <c r="B99" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C103)),Curs!C103,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C99)),Curs!C99,"")</f>
         <v/>
       </c>
       <c r="C99" s="10"/>
@@ -15693,11 +15693,11 @@
       <c r="F99" s="10"/>
       <c r="G99" s="10"/>
       <c r="H99" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C103)),ROUND(SUM(C99:G99),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C99)),ROUND(SUM(C99:G99),0),"")</f>
         <v/>
       </c>
       <c r="I99" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C103)),
+        <f>IF(NOT(ISBLANK(Curs!C99)),
 IF(H99=0,"n/p",
 IF(AND(H99&gt;=$J$3,H99&lt;=$K$3),$L$3,
 IF(AND(H99&gt;=$J$4,H99&lt;=$K$4),$L$4,
@@ -15714,11 +15714,11 @@
     </row>
     <row r="100" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A100" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B104)),Curs!B104,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B100)),Curs!B100,"")</f>
         <v/>
       </c>
       <c r="B100" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C104)),Curs!C104,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C100)),Curs!C100,"")</f>
         <v/>
       </c>
       <c r="C100" s="10"/>
@@ -15727,11 +15727,11 @@
       <c r="F100" s="10"/>
       <c r="G100" s="10"/>
       <c r="H100" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C104)),ROUND(SUM(C100:G100),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C100)),ROUND(SUM(C100:G100),0),"")</f>
         <v/>
       </c>
       <c r="I100" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C104)),
+        <f>IF(NOT(ISBLANK(Curs!C100)),
 IF(H100=0,"n/p",
 IF(AND(H100&gt;=$J$3,H100&lt;=$K$3),$L$3,
 IF(AND(H100&gt;=$J$4,H100&lt;=$K$4),$L$4,
@@ -15748,11 +15748,11 @@
     </row>
     <row r="101" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A101" s="30" t="str">
-        <f>IF(NOT(ISBLANK(Curs!B105)),Curs!B105,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!B101)),Curs!B101,"")</f>
         <v/>
       </c>
       <c r="B101" s="31" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C105)),Curs!C105,"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C101)),Curs!C101,"")</f>
         <v/>
       </c>
       <c r="C101" s="10"/>
@@ -15761,11 +15761,11 @@
       <c r="F101" s="10"/>
       <c r="G101" s="10"/>
       <c r="H101" s="24" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C105)),ROUND(SUM(C101:G101),0),"")</f>
+        <f>IF(NOT(ISBLANK(Curs!C101)),ROUND(SUM(C101:G101),0),"")</f>
         <v/>
       </c>
       <c r="I101" s="23" t="str">
-        <f>IF(NOT(ISBLANK(Curs!C105)),
+        <f>IF(NOT(ISBLANK(Curs!C101)),
 IF(H101=0,"n/p",
 IF(AND(H101&gt;=$J$3,H101&lt;=$K$3),$L$3,
 IF(AND(H101&gt;=$J$4,H101&lt;=$K$4),$L$4,
@@ -15776,6 +15776,122 @@
 IF(AND(H101&gt;=$J$9,H101&lt;=$K$9),$L$9,
 IF(AND(H101&gt;=$J$10,H101&lt;=$K$10),$L$10,
 IF(AND(H101&gt;=$J$11,H101&lt;=$K$11),$L$11)))))))))),
+"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="A102" s="30" t="str">
+        <f>IF(NOT(ISBLANK(Curs!B102)),Curs!B102,"")</f>
+        <v/>
+      </c>
+      <c r="B102" s="31" t="str">
+        <f>IF(NOT(ISBLANK(Curs!C102)),Curs!C102,"")</f>
+        <v/>
+      </c>
+      <c r="H102" s="24" t="str">
+        <f>IF(NOT(ISBLANK(Curs!C102)),ROUND(SUM(C102:G102),0),"")</f>
+        <v/>
+      </c>
+      <c r="I102" s="23" t="str">
+        <f>IF(NOT(ISBLANK(Curs!C102)),
+IF(H102=0,"n/p",
+IF(AND(H102&gt;=$J$3,H102&lt;=$K$3),$L$3,
+IF(AND(H102&gt;=$J$4,H102&lt;=$K$4),$L$4,
+IF(AND(H102&gt;=$J$5,H102&lt;=$K$5),$L$5,
+IF(AND(H102&gt;=$J$6,H102&lt;=$K$6),$L$6,
+IF(AND(H102&gt;=$J$7,H102&lt;=$K$7),$L$7,
+IF(AND(H102&gt;=$J$8,H102&lt;=$K$8),$L$8,
+IF(AND(H102&gt;=$J$9,H102&lt;=$K$9),$L$9,
+IF(AND(H102&gt;=$J$10,H102&lt;=$K$10),$L$10,
+IF(AND(H102&gt;=$J$11,H102&lt;=$K$11),$L$11)))))))))),
+"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="A103" s="30" t="str">
+        <f>IF(NOT(ISBLANK(Curs!B103)),Curs!B103,"")</f>
+        <v/>
+      </c>
+      <c r="B103" s="31" t="str">
+        <f>IF(NOT(ISBLANK(Curs!C103)),Curs!C103,"")</f>
+        <v/>
+      </c>
+      <c r="H103" s="24" t="str">
+        <f>IF(NOT(ISBLANK(Curs!C103)),ROUND(SUM(C103:G103),0),"")</f>
+        <v/>
+      </c>
+      <c r="I103" s="23" t="str">
+        <f>IF(NOT(ISBLANK(Curs!C103)),
+IF(H103=0,"n/p",
+IF(AND(H103&gt;=$J$3,H103&lt;=$K$3),$L$3,
+IF(AND(H103&gt;=$J$4,H103&lt;=$K$4),$L$4,
+IF(AND(H103&gt;=$J$5,H103&lt;=$K$5),$L$5,
+IF(AND(H103&gt;=$J$6,H103&lt;=$K$6),$L$6,
+IF(AND(H103&gt;=$J$7,H103&lt;=$K$7),$L$7,
+IF(AND(H103&gt;=$J$8,H103&lt;=$K$8),$L$8,
+IF(AND(H103&gt;=$J$9,H103&lt;=$K$9),$L$9,
+IF(AND(H103&gt;=$J$10,H103&lt;=$K$10),$L$10,
+IF(AND(H103&gt;=$J$11,H103&lt;=$K$11),$L$11)))))))))),
+"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="A104" s="30" t="str">
+        <f>IF(NOT(ISBLANK(Curs!B104)),Curs!B104,"")</f>
+        <v/>
+      </c>
+      <c r="B104" s="31" t="str">
+        <f>IF(NOT(ISBLANK(Curs!C104)),Curs!C104,"")</f>
+        <v/>
+      </c>
+      <c r="H104" s="24" t="str">
+        <f>IF(NOT(ISBLANK(Curs!C104)),ROUND(SUM(C104:G104),0),"")</f>
+        <v/>
+      </c>
+      <c r="I104" s="23" t="str">
+        <f>IF(NOT(ISBLANK(Curs!C104)),
+IF(H104=0,"n/p",
+IF(AND(H104&gt;=$J$3,H104&lt;=$K$3),$L$3,
+IF(AND(H104&gt;=$J$4,H104&lt;=$K$4),$L$4,
+IF(AND(H104&gt;=$J$5,H104&lt;=$K$5),$L$5,
+IF(AND(H104&gt;=$J$6,H104&lt;=$K$6),$L$6,
+IF(AND(H104&gt;=$J$7,H104&lt;=$K$7),$L$7,
+IF(AND(H104&gt;=$J$8,H104&lt;=$K$8),$L$8,
+IF(AND(H104&gt;=$J$9,H104&lt;=$K$9),$L$9,
+IF(AND(H104&gt;=$J$10,H104&lt;=$K$10),$L$10,
+IF(AND(H104&gt;=$J$11,H104&lt;=$K$11),$L$11)))))))))),
+"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="A105" s="30" t="str">
+        <f>IF(NOT(ISBLANK(Curs!B105)),Curs!B105,"")</f>
+        <v/>
+      </c>
+      <c r="B105" s="31" t="str">
+        <f>IF(NOT(ISBLANK(Curs!C105)),Curs!C105,"")</f>
+        <v/>
+      </c>
+      <c r="H105" s="24" t="str">
+        <f>IF(NOT(ISBLANK(Curs!C105)),ROUND(SUM(C105:G105),0),"")</f>
+        <v/>
+      </c>
+      <c r="I105" s="23" t="str">
+        <f>IF(NOT(ISBLANK(Curs!C105)),
+IF(H105=0,"n/p",
+IF(AND(H105&gt;=$J$3,H105&lt;=$K$3),$L$3,
+IF(AND(H105&gt;=$J$4,H105&lt;=$K$4),$L$4,
+IF(AND(H105&gt;=$J$5,H105&lt;=$K$5),$L$5,
+IF(AND(H105&gt;=$J$6,H105&lt;=$K$6),$L$6,
+IF(AND(H105&gt;=$J$7,H105&lt;=$K$7),$L$7,
+IF(AND(H105&gt;=$J$8,H105&lt;=$K$8),$L$8,
+IF(AND(H105&gt;=$J$9,H105&lt;=$K$9),$L$9,
+IF(AND(H105&gt;=$J$10,H105&lt;=$K$10),$L$10,
+IF(AND(H105&gt;=$J$11,H105&lt;=$K$11),$L$11)))))))))),
 "")</f>
         <v/>
       </c>
